--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU_05/HRM/post DDV_HRM-2031-0200/Panel 02/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU05_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.96092</v>
+        <v>17.09837</v>
       </c>
       <c r="D2" t="n">
-        <v>17.04677</v>
+        <v>16.84935</v>
       </c>
       <c r="E2" t="n">
-        <v>16.89347</v>
+        <v>17.04636</v>
       </c>
       <c r="F2" t="n">
-        <v>43.68497</v>
+        <v>42.94988</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05158</v>
+        <v>0.05192</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84858</v>
+        <v>1.83826</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.06695</v>
+        <v>16.85456</v>
       </c>
       <c r="D3" t="n">
-        <v>16.86455</v>
+        <v>16.61681</v>
       </c>
       <c r="E3" t="n">
-        <v>17.11371</v>
+        <v>16.72258</v>
       </c>
       <c r="F3" t="n">
-        <v>44.46718</v>
+        <v>43.87133</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05159</v>
+        <v>0.05104</v>
       </c>
       <c r="H3" t="n">
-        <v>1.85977</v>
+        <v>1.82431</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.09247</v>
+        <v>17.22793</v>
       </c>
       <c r="D4" t="n">
-        <v>16.5575</v>
+        <v>17.00083</v>
       </c>
       <c r="E4" t="n">
-        <v>16.90275</v>
+        <v>17.13969</v>
       </c>
       <c r="F4" t="n">
-        <v>43.33516</v>
+        <v>43.07464</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05172</v>
+        <v>0.05088</v>
       </c>
       <c r="H4" t="n">
-        <v>1.8276</v>
+        <v>1.86601</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.95414</v>
+        <v>16.80878</v>
       </c>
       <c r="D6" t="n">
-        <v>16.5817</v>
+        <v>16.35751</v>
       </c>
       <c r="E6" t="n">
-        <v>16.9341</v>
+        <v>16.66597</v>
       </c>
       <c r="F6" t="n">
-        <v>22.18148</v>
+        <v>21.99219</v>
       </c>
       <c r="G6" t="n">
-        <v>34.90508</v>
+        <v>34.42052</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.12923</v>
+        <v>16.87602</v>
       </c>
       <c r="D7" t="n">
-        <v>16.33116</v>
+        <v>16.45869</v>
       </c>
       <c r="E7" t="n">
-        <v>16.71193</v>
+        <v>16.87324</v>
       </c>
       <c r="F7" t="n">
-        <v>22.45834</v>
+        <v>22.16861</v>
       </c>
       <c r="G7" t="n">
-        <v>35.70596</v>
+        <v>34.76369</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.20817</v>
+        <v>16.90104</v>
       </c>
       <c r="D8" t="n">
-        <v>16.36588</v>
+        <v>16.10204</v>
       </c>
       <c r="E8" t="n">
-        <v>17.05643</v>
+        <v>16.62401</v>
       </c>
       <c r="F8" t="n">
-        <v>22.25642</v>
+        <v>22.16388</v>
       </c>
       <c r="G8" t="n">
-        <v>35.06464</v>
+        <v>35.07776</v>
       </c>
     </row>
   </sheetData>
